--- a/output/第10期計画_第9期施策別評価表と暫定評価ルール.xlsx
+++ b/output/第10期計画_第9期施策別評価表と暫定評価ルール.xlsx
@@ -4466,7 +4466,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>20.4％（98票中20票）</t>
+          <t>20.2％（99票中20票）</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">

--- a/output/第10期計画_第9期施策別評価表と暫定評価ルール.xlsx
+++ b/output/第10期計画_第9期施策別評価表と暫定評価ルール.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_成果評価" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_委員会用スコアカード" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_暫定評価" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_地域支援事業の評価の視点" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -58,7 +59,7 @@
       <sz val="8.5"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +84,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DEEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -156,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -193,6 +199,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6045,4 +6054,131 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>地域支援事業について第9期で確認した内容と第10期での評価</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>計画素案 第3章第2節から移したもの（令和8年9月29日のご指示による）。計画素案の本文には、第10期において何により評価するかを1段落で残している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>第9期における確認内容</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>第10期への反映</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>介護予防・日常生活支援総合事業</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>介護予防、生活支援、通いの場等の対象者実数、継続及び生活機能。通いの場は令和2年度で3箇所・151人</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>実人数、到達率、継続率、機能維持・改善を評価する。総合事業調査ベースを主系列とする</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="13" t="n"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>包括的支援事業</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>包括相談、医療介護連携、認知症、地域ケア会議等の支援実績</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>相談から支援接続、地域課題化及び施策反映を評価する</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="13" t="n"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>任意事業</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>家族介護支援、給付適正化、権利擁護等の実施状況</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>対象者への到達、利用成果及び改善効果を評価する。給付適正化はケアプラン点検及び医療情報との突合を第10期のアウトプット指標とする</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="13" t="n"/>
+    </row>
+    <row r="9" ht="66" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>注1）通いの場の令和2年度3箇所・151人は第9期計画による。令和6年度は総合事業の実施状況に関する調査により箇所数・参加実人数を把握している。
+注2）包括的支援事業のうち認知症総合支援事業は、決算の科目が4区分であり6事業別の内訳が得られないため、量による評価ができない。取組の回数によることとなる。
+注3）本シートは第9期の確認内容と第10期の評価の視点を対照するためのものであり、施策別の評価は01シートによる。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="C6:E6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>